--- a/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2022/4TO_TRIMESTRE/FRACCIONES XLII-XLVII/FRACC XLIII/LTAIPT_A63F43B.xlsx
+++ b/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2022/4TO_TRIMESTRE/FRACCIONES XLII-XLVII/FRACC XLIII/LTAIPT_A63F43B.xlsx
@@ -9,15 +9,23 @@
   <sheets>
     <sheet name="Informacion" sheetId="1" r:id="rId1"/>
     <sheet name="Tabla_437050" sheetId="2" r:id="rId2"/>
-    <sheet name="Tabla_437051" sheetId="3" r:id="rId3"/>
-    <sheet name="Tabla_437052" sheetId="4" r:id="rId4"/>
+    <sheet name="Hidden_1_Tabla_437050" sheetId="3" r:id="rId3"/>
+    <sheet name="Tabla_437051" sheetId="4" r:id="rId4"/>
+    <sheet name="Hidden_1_Tabla_437051" sheetId="5" r:id="rId5"/>
+    <sheet name="Tabla_437052" sheetId="6" r:id="rId6"/>
+    <sheet name="Hidden_1_Tabla_437052" sheetId="7" r:id="rId7"/>
   </sheets>
+  <definedNames>
+    <definedName name="Hidden_1_Tabla_4370505">Hidden_1_Tabla_437050!$A$1:$A$2</definedName>
+    <definedName name="Hidden_1_Tabla_4370515">Hidden_1_Tabla_437051!$A$1:$A$2</definedName>
+    <definedName name="Hidden_1_Tabla_4370525">Hidden_1_Tabla_437052!$A$1:$A$2</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="74">
   <si>
     <t>49015</t>
   </si>
@@ -121,37 +129,31 @@
     <t>Nota</t>
   </si>
   <si>
-    <t>AC1B46F59BC3787ED5C1D39F48E7795D</t>
-  </si>
-  <si>
-    <t>2022</t>
-  </si>
-  <si>
-    <t>01/10/2022</t>
-  </si>
-  <si>
-    <t>31/12/2022</t>
-  </si>
-  <si>
-    <t>4867639</t>
+    <t>9387996C1507AA981AB99899812BE75C</t>
+  </si>
+  <si>
+    <t>2023</t>
+  </si>
+  <si>
+    <t>01/01/2023</t>
+  </si>
+  <si>
+    <t>31/03/2023</t>
+  </si>
+  <si>
+    <t>6400940</t>
   </si>
   <si>
     <t>Departamento de Programación y Presupuesto</t>
   </si>
   <si>
-    <t>13/01/2023</t>
+    <t>25/04/2023</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>4503367</t>
-  </si>
-  <si>
-    <t>3001803</t>
-  </si>
-  <si>
-    <t>2437946</t>
+    <t>9</t>
   </si>
   <si>
     <t>56532</t>
@@ -163,6 +165,9 @@
     <t>56534</t>
   </si>
   <si>
+    <t>77788</t>
+  </si>
+  <si>
     <t>56535</t>
   </si>
   <si>
@@ -178,10 +183,13 @@
     <t>Segundo apellido</t>
   </si>
   <si>
+    <t>Sexo (catálogo)</t>
+  </si>
+  <si>
     <t>Cargo de los(as) servidores(as) públicos(as) de recibir los ingresos</t>
   </si>
   <si>
-    <t>BD533A7E70A97C7AA262B5DEF6D156DB</t>
+    <t>1B5261E07E6B22D7E2C45F5FCC24E564</t>
   </si>
   <si>
     <t>Darwin</t>
@@ -196,13 +204,10 @@
     <t>Director General</t>
   </si>
   <si>
-    <t>2E92E411A2D857C04AB42883E9EFAD2E</t>
-  </si>
-  <si>
-    <t>D47CFD6EB985D8BDE0558E694B8FA929</t>
-  </si>
-  <si>
-    <t>37482C56BEDEBB4BCFE36E9D34E24075</t>
+    <t>Hombre</t>
+  </si>
+  <si>
+    <t>Mujer</t>
   </si>
   <si>
     <t>56536</t>
@@ -214,22 +219,16 @@
     <t>56538</t>
   </si>
   <si>
+    <t>77785</t>
+  </si>
+  <si>
     <t>56539</t>
   </si>
   <si>
     <t xml:space="preserve">Cargo de los(as) servidores(as) públicos(as) que sea responsable de administrar los recursos </t>
   </si>
   <si>
-    <t>BD533A7E70A97C7AC640A041E041D433</t>
-  </si>
-  <si>
-    <t>9314D0918B4DF461CD8C9A359594CD57</t>
-  </si>
-  <si>
-    <t>2B18AD85B75244BC5FFD6F3013976759</t>
-  </si>
-  <si>
-    <t>1E260D1AB0F4122DFC91B488197E840C</t>
+    <t>1B5261E07E6B22D7616B3C29F7D4C768</t>
   </si>
   <si>
     <t>56540</t>
@@ -241,22 +240,16 @@
     <t>56542</t>
   </si>
   <si>
+    <t>77789</t>
+  </si>
+  <si>
     <t>56543</t>
   </si>
   <si>
     <t>Cargo de los(as) servidores(as) públicos(as) que sea(s) responsable(s) de ejercerlo</t>
   </si>
   <si>
-    <t>BD533A7E70A97C7A39FF5029A37D84BE</t>
-  </si>
-  <si>
-    <t>ED9DC894096E88F616B32B0B2FA71EB6</t>
-  </si>
-  <si>
-    <t>F5B2F715CA004E9235535720941B500D</t>
-  </si>
-  <si>
-    <t>D74AD2B7B05C2EA2B4121315C2150BFF</t>
+    <t>D786CDA928AB3B467B8BDC2F40633F0A</t>
   </si>
 </sst>
 </file>
@@ -655,7 +648,7 @@
   <dimension ref="A1:K8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="35.85546875" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="35.42578125" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="36.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="5" width="38.5703125" bestFit="1" customWidth="1"/>
@@ -866,18 +859,19 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="36.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="35.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="17" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="19.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="70.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="70.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="C1" t="s">
         <v>6</v>
       </c>
@@ -888,42 +882,51 @@
         <v>6</v>
       </c>
       <c r="F1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="C2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E2" t="s">
         <v>44</v>
       </c>
-      <c r="D2" t="s">
+      <c r="F2" t="s">
         <v>45</v>
       </c>
-      <c r="E2" t="s">
+      <c r="G2" t="s">
         <v>46</v>
       </c>
-      <c r="F2" t="s">
+    </row>
+    <row r="3" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
         <v>47</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>48</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>37</v>
       </c>
@@ -940,77 +943,167 @@
         <v>56</v>
       </c>
       <c r="F4" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="G4" s="3" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>57</v>
-      </c>
-    </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="F4:F201">
+      <formula1>Hidden_1_Tabla_4370505</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="35.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="98.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="C1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="C2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E2" t="s">
+        <v>62</v>
+      </c>
+      <c r="F2" t="s">
+        <v>63</v>
+      </c>
+      <c r="G2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="F4:F201">
+      <formula1>Hidden_1_Tabla_4370515</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.42578125" bestFit="1" customWidth="1"/>
@@ -1018,10 +1111,11 @@
     <col min="3" max="3" width="12.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="17" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="19.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="98.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="87.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="C1" t="s">
         <v>6</v>
       </c>
@@ -1032,47 +1126,56 @@
         <v>6</v>
       </c>
       <c r="F1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="C2" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="D2" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="E2" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="F2" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+        <v>70</v>
+      </c>
+      <c r="G2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="F3" s="1" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G3" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>37</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>54</v>
@@ -1084,211 +1187,35 @@
         <v>56</v>
       </c>
       <c r="F4" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="G4" s="3" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>57</v>
-      </c>
-    </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="F4:F201">
+      <formula1>Hidden_1_Tabla_4370525</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:A2"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="35.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="87.28515625" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
-    <row r="1" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C2" t="s">
-        <v>70</v>
-      </c>
-      <c r="D2" t="s">
-        <v>71</v>
-      </c>
-      <c r="E2" t="s">
-        <v>72</v>
-      </c>
-      <c r="F2" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>57</v>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>59</v>
       </c>
     </row>
   </sheetData>
